--- a/regles/REGLES_FKS.xlsx
+++ b/regles/REGLES_FKS.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ordre et choix des colonnes : journal, date, piece, compte, tiers, libelle, debit, credit</t>
+          <t>ordre et choix des colonnes (séparées par | ; ou ,) : journal, date, piece, compte, tiers, libelle, debit, credit</t>
         </is>
       </c>
     </row>

--- a/regles/REGLES_FKS.xlsx
+++ b/regles/REGLES_FKS.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ordre et choix des colonnes (séparées par | ; ou ,) : journal, date, piece, compte, tiers, libelle, debit, credit</t>
+          <t>ordre et choix des colonnes : journal, date, piece, compte, tiers, libelle, debit, credit</t>
         </is>
       </c>
     </row>
